--- a/artfynd/A 54420-2021 artfynd.xlsx
+++ b/artfynd/A 54420-2021 artfynd.xlsx
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118704094</v>
+        <v>118704096</v>
       </c>
       <c r="B5" t="n">
-        <v>97763</v>
+        <v>97846</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,25 +1015,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475381</v>
+        <v>475382</v>
       </c>
       <c r="R5" t="n">
-        <v>6853668</v>
+        <v>6853672</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118704096</v>
+        <v>118707839</v>
       </c>
       <c r="B6" t="n">
-        <v>97846</v>
+        <v>79566</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,38 +1131,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hälltjärnen – Övre Gryssjön, Hjd</t>
+          <t>Hälltjärnen-Övre Gryssjön, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475382</v>
+        <v>475041</v>
       </c>
       <c r="R6" t="n">
-        <v>6853672</v>
+        <v>6853504</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,22 +1189,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:59</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:59</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,12 +1209,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Råghall, Klara Li Yngve, Håkan Thenander</t>
+          <t>Staffan Petré, Johanna Dalmalm, Johan Råghall, Håkan Thenander, Miriam Schenk, Benny Öwre</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1341,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118707839</v>
+        <v>118704094</v>
       </c>
       <c r="B8" t="n">
-        <v>79566</v>
+        <v>97763</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,38 +1343,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hälltjärnen-Övre Gryssjön, Hjd</t>
+          <t>Hälltjärnen – Övre Gryssjön, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475041</v>
+        <v>475381</v>
       </c>
       <c r="R8" t="n">
-        <v>6853504</v>
+        <v>6853668</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,12 +1401,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1431,12 +1431,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Staffan Petré</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Staffan Petré, Johanna Dalmalm, Johan Råghall, Håkan Thenander, Miriam Schenk, Benny Öwre</t>
+          <t>Johan Råghall, Klara Li Yngve, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 54420-2021 artfynd.xlsx
+++ b/artfynd/A 54420-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118707852</v>
+        <v>118704096</v>
       </c>
       <c r="B2" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hälltjärnen-Övre Gryssjön, Hjd</t>
+          <t>Hälltjärnen – Övre Gryssjön, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474992</v>
+        <v>475382</v>
       </c>
       <c r="R2" t="n">
-        <v>6853601</v>
+        <v>6853672</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,12 +775,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Staffan Petré</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Staffan Petré, Johanna Dalmalm, Johan Råghall, Håkan Thenander, Miriam Schenk, Benny Öwre</t>
+          <t>Johan Råghall, Håkan Thenander, Klara Li Yngve</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118703995</v>
+        <v>118703990</v>
       </c>
       <c r="B3" t="n">
-        <v>79565</v>
+        <v>79566</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -876,7 +886,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Klara Li Yngve, Håkan Thenander, Johan Råghall, Staffan Petré, Gabriella Westberg, Johanna Dalmalm</t>
+          <t>Klara Li Yngve, Johanna Dalmalm, Gabriella Westberg, Staffan Petré, Johan Råghall, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118704097</v>
+        <v>118704094</v>
       </c>
       <c r="B4" t="n">
-        <v>79565</v>
+        <v>97763</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475315</v>
+        <v>475381</v>
       </c>
       <c r="R4" t="n">
-        <v>6853706</v>
+        <v>6853668</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,7 +972,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -972,7 +982,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,7 +1002,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Råghall, Klara Li Yngve, Håkan Thenander</t>
+          <t>Johan Råghall, Håkan Thenander, Klara Li Yngve</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1003,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118704096</v>
+        <v>118707839</v>
       </c>
       <c r="B5" t="n">
-        <v>97846</v>
+        <v>79566</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,38 +1025,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hälltjärnen – Övre Gryssjön, Hjd</t>
+          <t>Hälltjärnen-Övre Gryssjön, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475382</v>
+        <v>475041</v>
       </c>
       <c r="R5" t="n">
-        <v>6853672</v>
+        <v>6853504</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,22 +1083,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:59</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:59</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,12 +1103,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Råghall, Klara Li Yngve, Håkan Thenander</t>
+          <t>Staffan Petré, Johanna Dalmalm, Johan Råghall, Håkan Thenander, Miriam Schenk, Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118707839</v>
+        <v>118707852</v>
       </c>
       <c r="B6" t="n">
-        <v>79566</v>
+        <v>79565</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475041</v>
+        <v>474992</v>
       </c>
       <c r="R6" t="n">
-        <v>6853504</v>
+        <v>6853601</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118703990</v>
+        <v>118704097</v>
       </c>
       <c r="B7" t="n">
-        <v>79566</v>
+        <v>79565</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,34 +1241,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hjd</t>
+          <t>Hälltjärnen – Övre Gryssjön, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475375</v>
+        <v>475315</v>
       </c>
       <c r="R7" t="n">
-        <v>6853683</v>
+        <v>6853706</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,9 +1298,19 @@
           <t>2024-07-26</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,12 +1325,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Klara Li Yngve</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Klara Li Yngve, Håkan Thenander, Johan Råghall, Staffan Petré, Gabriella Westberg, Johanna Dalmalm</t>
+          <t>Johan Råghall, Håkan Thenander, Klara Li Yngve</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1331,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118704094</v>
+        <v>118703995</v>
       </c>
       <c r="B8" t="n">
-        <v>97763</v>
+        <v>79565</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,38 +1353,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hälltjärnen – Övre Gryssjön, Hjd</t>
+          <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475381</v>
+        <v>475375</v>
       </c>
       <c r="R8" t="n">
-        <v>6853668</v>
+        <v>6853683</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,19 +1414,9 @@
           <t>2024-07-26</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>16:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1431,12 +1431,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Klara Li Yngve</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Råghall, Klara Li Yngve, Håkan Thenander</t>
+          <t>Klara Li Yngve, Gabriella Westberg, Johanna Dalmalm, Staffan Petré, Johan Råghall, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 54420-2021 artfynd.xlsx
+++ b/artfynd/A 54420-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118704096</v>
+        <v>118703990</v>
       </c>
       <c r="B2" t="n">
-        <v>97846</v>
+        <v>79573</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hälltjärnen – Övre Gryssjön, Hjd</t>
+          <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475382</v>
+        <v>475375</v>
       </c>
       <c r="R2" t="n">
-        <v>6853672</v>
+        <v>6853683</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +748,9 @@
           <t>2024-07-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:59</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,12 +765,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Klara Li Yngve</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Råghall, Håkan Thenander, Klara Li Yngve</t>
+          <t>Klara Li Yngve, Håkan Thenander, Johan Råghall, Staffan Petré, Gabriella Westberg, Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -791,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118703990</v>
+        <v>118704097</v>
       </c>
       <c r="B3" t="n">
-        <v>79566</v>
+        <v>79572</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,34 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hjd</t>
+          <t>Hälltjärnen – Övre Gryssjön, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475375</v>
+        <v>475315</v>
       </c>
       <c r="R3" t="n">
-        <v>6853683</v>
+        <v>6853706</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,9 +854,19 @@
           <t>2024-07-26</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,12 +881,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Klara Li Yngve</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Klara Li Yngve, Johanna Dalmalm, Gabriella Westberg, Staffan Petré, Johan Råghall, Håkan Thenander</t>
+          <t>Johan Råghall, Klara Li Yngve, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118704094</v>
+        <v>118704096</v>
       </c>
       <c r="B4" t="n">
-        <v>97763</v>
+        <v>97853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475381</v>
+        <v>475382</v>
       </c>
       <c r="R4" t="n">
-        <v>6853668</v>
+        <v>6853672</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,7 +972,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Råghall, Håkan Thenander, Klara Li Yngve</t>
+          <t>Johan Råghall, Klara Li Yngve, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118707839</v>
+        <v>118704094</v>
       </c>
       <c r="B5" t="n">
-        <v>79566</v>
+        <v>97770</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,38 +1025,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hälltjärnen-Övre Gryssjön, Hjd</t>
+          <t>Hälltjärnen – Övre Gryssjön, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475041</v>
+        <v>475381</v>
       </c>
       <c r="R5" t="n">
-        <v>6853504</v>
+        <v>6853668</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,12 +1083,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,12 +1113,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Staffan Petré</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Staffan Petré, Johanna Dalmalm, Johan Råghall, Håkan Thenander, Miriam Schenk, Benny Öwre</t>
+          <t>Johan Råghall, Klara Li Yngve, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1119,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118707852</v>
+        <v>118707839</v>
       </c>
       <c r="B6" t="n">
-        <v>79565</v>
+        <v>79573</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1145,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1159,10 +1169,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474992</v>
+        <v>475041</v>
       </c>
       <c r="R6" t="n">
-        <v>6853601</v>
+        <v>6853504</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118704097</v>
+        <v>118703995</v>
       </c>
       <c r="B7" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,14 +1271,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hälltjärnen – Övre Gryssjön, Hjd</t>
+          <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475315</v>
+        <v>475375</v>
       </c>
       <c r="R7" t="n">
-        <v>6853706</v>
+        <v>6853683</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,19 +1308,9 @@
           <t>2024-07-26</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:57</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,12 +1325,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Klara Li Yngve</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johan Råghall, Håkan Thenander, Klara Li Yngve</t>
+          <t>Klara Li Yngve, Håkan Thenander, Johan Råghall, Staffan Petré, Gabriella Westberg, Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118703995</v>
+        <v>118707852</v>
       </c>
       <c r="B8" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,14 +1377,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hjd</t>
+          <t>Hälltjärnen-Övre Gryssjön, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475375</v>
+        <v>474992</v>
       </c>
       <c r="R8" t="n">
-        <v>6853683</v>
+        <v>6853601</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1431,12 +1431,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Klara Li Yngve</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Klara Li Yngve, Gabriella Westberg, Johanna Dalmalm, Staffan Petré, Johan Råghall, Håkan Thenander</t>
+          <t>Staffan Petré, Johanna Dalmalm, Johan Råghall, Håkan Thenander, Miriam Schenk, Benny Öwre</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1450,7 +1450,7 @@
         <v>118689069</v>
       </c>
       <c r="B9" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 54420-2021 artfynd.xlsx
+++ b/artfynd/A 54420-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118703990</v>
+        <v>118707852</v>
       </c>
       <c r="B2" t="n">
-        <v>79573</v>
+        <v>79572</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hjd</t>
+          <t>Hälltjärnen-Övre Gryssjön, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475375</v>
+        <v>474992</v>
       </c>
       <c r="R2" t="n">
-        <v>6853683</v>
+        <v>6853601</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,12 +765,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Klara Li Yngve</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Klara Li Yngve, Håkan Thenander, Johan Råghall, Staffan Petré, Gabriella Westberg, Johanna Dalmalm</t>
+          <t>Staffan Petré, Johanna Dalmalm, Johan Råghall, Håkan Thenander, Miriam Schenk, Benny Öwre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118704097</v>
+        <v>118704094</v>
       </c>
       <c r="B3" t="n">
-        <v>79572</v>
+        <v>97770</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475315</v>
+        <v>475381</v>
       </c>
       <c r="R3" t="n">
-        <v>6853706</v>
+        <v>6853668</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118704096</v>
+        <v>118707839</v>
       </c>
       <c r="B4" t="n">
-        <v>97853</v>
+        <v>79573</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,38 +909,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hälltjärnen – Övre Gryssjön, Hjd</t>
+          <t>Hälltjärnen-Övre Gryssjön, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475382</v>
+        <v>475041</v>
       </c>
       <c r="R4" t="n">
-        <v>6853672</v>
+        <v>6853504</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,22 +967,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:59</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:59</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,12 +987,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Råghall, Klara Li Yngve, Håkan Thenander</t>
+          <t>Staffan Petré, Johanna Dalmalm, Johan Råghall, Håkan Thenander, Miriam Schenk, Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1013,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118704094</v>
+        <v>118704097</v>
       </c>
       <c r="B5" t="n">
-        <v>97770</v>
+        <v>79572</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,25 +1015,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1053,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475381</v>
+        <v>475315</v>
       </c>
       <c r="R5" t="n">
-        <v>6853668</v>
+        <v>6853706</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1098,7 +1088,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118707839</v>
+        <v>118703995</v>
       </c>
       <c r="B6" t="n">
-        <v>79573</v>
+        <v>79572</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,34 +1135,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hälltjärnen-Övre Gryssjön, Hjd</t>
+          <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475041</v>
+        <v>475375</v>
       </c>
       <c r="R6" t="n">
-        <v>6853504</v>
+        <v>6853683</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,12 +1189,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,12 +1209,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Staffan Petré</t>
+          <t>Klara Li Yngve</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Staffan Petré, Johanna Dalmalm, Johan Råghall, Håkan Thenander, Miriam Schenk, Benny Öwre</t>
+          <t>Klara Li Yngve, Håkan Thenander, Johan Råghall, Staffan Petré, Gabriella Westberg, Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1235,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118703995</v>
+        <v>118704096</v>
       </c>
       <c r="B7" t="n">
-        <v>79572</v>
+        <v>97853</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,38 +1237,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hälltjärnen, Hjd</t>
+          <t>Hälltjärnen – Övre Gryssjön, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475375</v>
+        <v>475382</v>
       </c>
       <c r="R7" t="n">
-        <v>6853683</v>
+        <v>6853672</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,9 +1298,19 @@
           <t>2024-07-26</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,12 +1325,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Klara Li Yngve</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Klara Li Yngve, Håkan Thenander, Johan Råghall, Staffan Petré, Gabriella Westberg, Johanna Dalmalm</t>
+          <t>Johan Råghall, Klara Li Yngve, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118707852</v>
+        <v>118703990</v>
       </c>
       <c r="B8" t="n">
-        <v>79572</v>
+        <v>79573</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,34 +1357,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hälltjärnen-Övre Gryssjön, Hjd</t>
+          <t>Hälltjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474992</v>
+        <v>475375</v>
       </c>
       <c r="R8" t="n">
-        <v>6853601</v>
+        <v>6853683</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1431,12 +1431,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Staffan Petré</t>
+          <t>Klara Li Yngve</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Staffan Petré, Johanna Dalmalm, Johan Råghall, Håkan Thenander, Miriam Schenk, Benny Öwre</t>
+          <t>Klara Li Yngve, Håkan Thenander, Johan Råghall, Staffan Petré, Gabriella Westberg, Johanna Dalmalm</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
